--- a/Requisitioner.xlsx
+++ b/Requisitioner.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Downloads\Raawa Generator_3\Raawa Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8151C95-6C66-404F-8668-17B9177C24A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A703E82-B7B3-4F17-A51F-22150D8616E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>Requisitioner</t>
   </si>
@@ -79,6 +90,18 @@
   </si>
   <si>
     <t>MIN</t>
+  </si>
+  <si>
+    <t>EUL MIGRATION - ADVANCE SURVEY</t>
+  </si>
+  <si>
+    <t>Miguel Evangelista</t>
+  </si>
+  <si>
+    <t>NTG/B&amp;D/NBSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09176884753</t>
   </si>
 </sst>
 </file>
@@ -462,7 +485,7 @@
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
     <col min="3" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="18.26953125" customWidth="1"/>
-    <col min="6" max="6" width="26.36328125" customWidth="1"/>
+    <col min="6" max="6" width="32.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -542,22 +565,50 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10009038</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10009038</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>

--- a/Requisitioner.xlsx
+++ b/Requisitioner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Downloads\Raawa Generator_3\Raawa Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A703E82-B7B3-4F17-A51F-22150D8616E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CEF793-4374-4BD8-8D14-CA3386D4CADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>Requisitioner</t>
   </si>
@@ -102,6 +102,18 @@
   </si>
   <si>
     <t xml:space="preserve"> 09176884753</t>
+  </si>
+  <si>
+    <t>DISMANTLING</t>
+  </si>
+  <si>
+    <t>SPBD</t>
+  </si>
+  <si>
+    <t>B2B_B2C</t>
+  </si>
+  <si>
+    <t>B2C_EUL MIGRATION</t>
   </si>
 </sst>
 </file>
@@ -178,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,15 +201,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" customWidth="1"/>
@@ -489,13 +502,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -513,10 +526,10 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -615,63 +628,120 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Requisitioner.xlsx
+++ b/Requisitioner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Downloads\Raawa Generator_3\Raawa Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CEF793-4374-4BD8-8D14-CA3386D4CADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AC287F-18D8-47DB-88B7-49E033A94851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="26">
   <si>
     <t>Requisitioner</t>
   </si>
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -210,7 +210,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -624,10 +623,18 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>7796</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
@@ -639,10 +646,16 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
@@ -654,10 +667,18 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>7796</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
       </c>
@@ -669,10 +690,16 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
@@ -684,10 +711,18 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>7796</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
       </c>
@@ -699,10 +734,16 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
@@ -714,10 +755,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>7796</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>9</v>
       </c>
@@ -729,10 +778,16 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
       </c>

--- a/Requisitioner.xlsx
+++ b/Requisitioner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\N-20W1PF3VP3VC-Data\rabanes\Downloads\Raawa Generator_3\Raawa Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AC287F-18D8-47DB-88B7-49E033A94851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E1592A-8806-42E4-86D4-441337F1E93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="25">
   <si>
     <t>Requisitioner</t>
   </si>
@@ -53,15 +53,9 @@
     <t>Contact No.</t>
   </si>
   <si>
-    <t>T8 BAPE</t>
-  </si>
-  <si>
     <t>Territory no.</t>
   </si>
   <si>
-    <t>ARNULFO DOBLE</t>
-  </si>
-  <si>
     <t>Territory 7</t>
   </si>
   <si>
@@ -114,6 +108,9 @@
   </si>
   <si>
     <t>B2C_EUL MIGRATION</t>
+  </si>
+  <si>
+    <t>Leonilo D. Maputi Jr.</t>
   </si>
 </sst>
 </file>
@@ -523,279 +520,279 @@
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>10013334</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>7796</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>10009038</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <v>10009038</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10013334</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>7796</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10013334</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>7796</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10013334</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>7796</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10013334</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>7796</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
